--- a/importaciones_productos/FE30232 registro productos.xlsx
+++ b/importaciones_productos/FE30232 registro productos.xlsx
@@ -503,12 +503,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FAR10MAZUUn</t>
+          <t>FARAMBmL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FARMA 10ML AZUL</t>
+          <t>FARMA 5ML AMBAR</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -518,11 +518,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>682</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -536,12 +536,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GOTPIP55MUn</t>
+          <t>FARAZUmL</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>GOTERO PIPETA 55MM NEGRA</t>
+          <t>FARMA 10ML AZUL</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -551,11 +551,11 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>600</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="4">
@@ -569,12 +569,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PAS180BLAUn</t>
+          <t>FARAMBmL2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PASTILLERO 180ML BLANCO</t>
+          <t>FARMA 30ML AMBAR</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -584,11 +584,11 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>380</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="5">
@@ -602,12 +602,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>TAP38MSENUn</t>
+          <t>FARAMBmL3</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>TAPA 38MM SENCILLA BLANCA</t>
+          <t>FARMA 50ML AMBAR</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -617,11 +617,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>90</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="6">
@@ -635,12 +635,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FAR30MCRIUn</t>
+          <t>PASBLAmL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>FARMA 30ML CRISTAL</t>
+          <t>PASTILLERO 180ML BLANCO</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>660</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="7">
@@ -668,12 +668,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>GOTPIP77MNEGUn</t>
+          <t>FARCRImL</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GOTERO PIPETA 77MM NEGRO</t>
+          <t>FARMA 30ML CRISTAL</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -683,11 +683,11 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>600</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -701,12 +701,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GOTPIP77MNEGUn2</t>
+          <t>FARAZUmL2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>GOTERO PIPETA 77MM NEGRO</t>
+          <t>FARMA 30ML AZUL</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -716,11 +716,11 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>600</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -734,12 +734,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>FAR5MLAMBUn</t>
+          <t>TAP18MSEGUn</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>FARMA 5ML AMBAR</t>
+          <t>TAPA 18MM SEGURIDAD ECO BLANCA</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>420</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -767,12 +767,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TAP18MSEGUn</t>
+          <t>TAP18MAIRUn</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TAPA 18MM SEGURIDAD ECO BLANCA</t>
+          <t>TAPON 18MM AIREADOR BLANCO ECO</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>TAP18MAIRUn</t>
+          <t>GOTPIP55MUn</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>TAPON 18MM AIREADOR BLANCO ECO</t>
+          <t>GOTERO PIPETA 55MM NEGRA</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12">
@@ -833,12 +833,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>FAR30MAMBUn</t>
+          <t>GOTPIP77MUn</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>FARMA 30ML AMBAR</t>
+          <t>GOTERO PIPETA 77MM NEGRO</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>498</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13">
@@ -866,12 +866,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>GOTPIP77MUn</t>
+          <t>GOTPIP90MUn</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>GOTERO PIPETA 77MM NEGRO</t>
+          <t>GOTERO PIPETA 90MM NEGRO</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>FAR50MAMBUn</t>
+          <t>TAP38MSENUn</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>FARMA 50ML AMBAR</t>
+          <t>TAPA 38MM SENCILLA BLANCA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>730</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -932,12 +932,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>GOTPIP90MUn</t>
+          <t>GOTPIP77MNEGUn</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>GOTERO PIPETA 90MM NEGRO</t>
+          <t>GOTERO PIPETA 77MM NEGRO</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>FAR30MAZUUn</t>
+          <t>GOTPIP77MNEGUn2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>FARMA 30ML AZUL</t>
+          <t>GOTERO PIPETA 77MM NEGRO</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17">
